--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoanalistas-my.sharepoint.com/personal/jpuerta_afi_es/Documents/Documentos/Master Quant/Gestión de activos/Trabajo gestión cuantitativa/Trabajo_gestion_cuantitativa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelafinanzasaplicadas-my.sharepoint.com/personal/jolmedo_afiglobaleducation_es/Documents/Gestión Cuantitativa/Trabajo_gestion_cuantitativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_F25DC773A252ABDACC10489ED1D86CD45ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35E84211-18F9-4965-A5F4-091947CC2F0A}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC10489ED1D86CD45ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F5EDAA5-2DDC-4060-8023-871BDA7E06AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5"/>
     </row>
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5"/>
     </row>
